--- a/agrupaciones_arboles.xlsx
+++ b/agrupaciones_arboles.xlsx
@@ -61,51 +61,51 @@
     <t xml:space="preserve">≥ 793</t>
   </si>
   <si>
+    <t xml:space="preserve">G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G8</t>
+  </si>
+  <si>
     <t xml:space="preserve">G9</t>
   </si>
   <si>
+    <t xml:space="preserve">G11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">425–792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133–424</t>
+  </si>
+  <si>
     <t xml:space="preserve">G5</t>
   </si>
   <si>
+    <t xml:space="preserve">G10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40–132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1</t>
+  </si>
+  <si>
     <t xml:space="preserve">G4</t>
   </si>
   <si>
-    <t xml:space="preserve">G3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">425–792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133–424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G7</t>
+    <t xml:space="preserve">G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤ 39</t>
   </si>
   <si>
     <t xml:space="preserve">G2</t>
   </si>
   <si>
-    <t xml:space="preserve">40–132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≤ 39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G10</t>
-  </si>
-  <si>
     <t xml:space="preserve">Missing</t>
   </si>
   <si>
@@ -244,6 +244,9 @@
     <t xml:space="preserve">≥ 658</t>
   </si>
   <si>
+    <t xml:space="preserve">G12</t>
+  </si>
+  <si>
     <t xml:space="preserve">288–657</t>
   </si>
   <si>
@@ -254,9 +257,6 @@
   </si>
   <si>
     <t xml:space="preserve">≤ 37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G12</t>
   </si>
   <si>
     <t xml:space="preserve">154–287 a ≥ 658</t>
@@ -2670,144 +2670,144 @@
         <v>72</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H5" s="55" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="B6" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E7" s="57" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E8" s="60" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F8" s="60" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G8" s="61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="G9" s="62" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H9" s="62" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I9" s="62" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2815,28 +2815,28 @@
         <v>27</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="G10" s="62" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H10" s="62" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I10" s="62" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2870,7 +2870,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>71</v>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="63" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>79</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="64" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>79</v>
@@ -2969,13 +2969,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>81</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" s="20" t="n">
         <v>2918.24</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>82</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="67" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>83</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="68" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>84</v>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="69" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>85</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="70" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>81</v>
@@ -3167,13 +3167,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="71" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>84</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" s="20" t="n">
         <v>3750.24</v>
@@ -3200,13 +3200,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="72" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>85</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" s="20" t="n">
         <v>2959.84</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>87</v>
@@ -3373,28 +3373,28 @@
         <v>90</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="73" t="s">
+      <c r="G5" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>15</v>
-      </c>
-      <c r="G5" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3402,28 +3402,28 @@
         <v>91</v>
       </c>
       <c r="B6" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="73" t="s">
+      <c r="G6" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>15</v>
-      </c>
-      <c r="G6" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3431,28 +3431,28 @@
         <v>92</v>
       </c>
       <c r="B7" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="F7" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="76" t="s">
+      <c r="G7" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="76" t="s">
+      <c r="H7" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="77" t="s">
-        <v>14</v>
-      </c>
       <c r="I7" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3460,28 +3460,28 @@
         <v>93</v>
       </c>
       <c r="B8" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="75" t="s">
+      <c r="F8" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="76" t="s">
+      <c r="G8" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="76" t="s">
+      <c r="H8" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="77" t="s">
-        <v>14</v>
-      </c>
       <c r="I8" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3489,28 +3489,28 @@
         <v>94</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="H9" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="I9" s="78" t="s">
         <v>12</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="78" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3518,28 +3518,28 @@
         <v>27</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="H10" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="I10" s="78" t="s">
         <v>12</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="78" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3573,7 +3573,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>71</v>
@@ -3606,7 +3606,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="79" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>79</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>68</v>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="81" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>79</v>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="68" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>98</v>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>84</v>
@@ -3771,7 +3771,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="83" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>81</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="84" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>85</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>87</v>
